--- a/jogos_2025-06-28.xlsx
+++ b/jogos_2025-06-28.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.82</v>
+        <v>3.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.13</v>
+        <v>3.29</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2.5</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['50', '59']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45836.25</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.53</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.79</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.24</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.82</v>
+        <v>2.21</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.27</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>3.48</v>
+        <v>2.03</v>
       </c>
       <c r="U6" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA6" t="n">
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['9005']</t>
+          <t>['3', '90+4']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['45', '20', '90']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.01</v>
+        <v>2.83</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45836.25</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.8</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>1.77</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.21</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -1479,47 +1479,47 @@
         <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['3', '90+4']</t>
+          <t>['18', '6', '16', '64']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['45', '20', '90']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>2.95</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.83</v>
+        <v>1.32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>3.38</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45836.25</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="O9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.77</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['18', '6', '16', '64']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['50', '59']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45836.25</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.7</v>
+        <v>2.53</v>
       </c>
       <c r="M10" t="n">
-        <v>3.29</v>
+        <v>2.79</v>
       </c>
       <c r="N10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.83</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.09</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.43</v>
+        <v>3.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['9005']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45836.25</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>3.81</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.88</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.45</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1893,20 +1893,20 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['8', '23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.85</v>
+        <v>2.71</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45836.27083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="N12" t="n">
-        <v>3.81</v>
+        <v>2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '23']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.71</v>
+        <v>1.85</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45836.27083333334</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>3.52</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
         <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['85', '9014']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45836.29166666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.52</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
         <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>2.93</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.5</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI14" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45836.29166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.02</v>
+        <v>2.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.41</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.78</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
         <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>4.15</v>
+        <v>2.97</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Z16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['17', '25', '52']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['4503']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['39', '62']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45836.29166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>2.28</v>
       </c>
       <c r="O17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.62</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.65</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.05</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.58</v>
+        <v>4.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '38']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45836.29166666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="M18" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="O18" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['9005']</t>
+          <t>['85', '9014']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45836.29166666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="M19" t="n">
         <v>3.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X19" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['9005']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45836.29166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P20" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q20" t="n">
-        <v>4.78</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="Z20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['38', '9001']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AJ20" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['35', '45']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.62</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>2.86</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="O21" t="n">
-        <v>2.93</v>
+        <v>3.48</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3.14</v>
+        <v>2.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.58</v>
+        <v>3.26</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>3.86</v>
+        <v>2.81</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>4.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
@@ -3273,59 +3273,59 @@
         <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['38', '9001']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="M23" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="N23" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.79</v>
+        <v>3.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="T23" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.76</v>
+        <v>2.32</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3496,7 +3496,7 @@
         <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="M24" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
@@ -3540,16 +3540,16 @@
         <v>1.09</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X24" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
         <v>4.75</v>
@@ -3558,32 +3558,32 @@
         <v>1.18</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['12', '38']</t>
+          <t>['21', '40']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3610,22 +3610,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="M25" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O25" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['17', '25', '52']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG25" t="n">
         <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.81</v>
+        <v>3.04</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="O26" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>2.79</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['21', '40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.27</v>
+        <v>3.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="U27" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['4503']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['39', '62']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45836.29166666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="M28" t="n">
-        <v>2.97</v>
+        <v>3.59</v>
       </c>
       <c r="N28" t="n">
-        <v>2.31</v>
+        <v>3.71</v>
       </c>
       <c r="O28" t="n">
-        <v>3.48</v>
+        <v>2.24</v>
       </c>
       <c r="P28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA28" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['35', '45']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45836.29166666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,87 +4255,87 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4344,20 +4344,20 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['20', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45836.33333333334</v>
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH31" t="n">
         <v>3.3</v>
       </c>
-      <c r="N31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['12', '49', '63']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45836.33333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45836.33333333334</v>
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.9</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.55</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2</v>
       </c>
-      <c r="Q33" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90', '25']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45836.33333333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="M34" t="n">
         <v>3.55</v>
       </c>
       <c r="N34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.3</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.95</v>
-      </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['90', '25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['20', '86']</t>
         </is>
       </c>
       <c r="AG34" t="n">
         <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AI34" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45836.33333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,22 +5029,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="M36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N36" t="n">
         <v>3.6</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.77</v>
-      </c>
       <c r="O36" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.55</v>
+        <v>4.86</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="T36" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="U36" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W36" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="X36" t="n">
-        <v>4.4</v>
+        <v>2.68</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['12', '49', '63']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.85</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45836.33333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.58</v>
+        <v>5.2</v>
       </c>
       <c r="N41" t="n">
-        <v>1.64</v>
+        <v>8.6</v>
       </c>
       <c r="O41" t="n">
-        <v>5.41</v>
+        <v>1.73</v>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.29</v>
+        <v>8.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>2.95</v>
+        <v>4.75</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
+          <t>['30', '59']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG41" t="n">
-        <v>2.16</v>
+        <v>1.05</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.06</v>
+        <v>3.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45836.41666666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,91 +5803,91 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['30', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45836.41666666666</v>
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="M43" t="n">
         <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
         <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45836.41666666666</v>
@@ -6070,100 +6070,100 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45836.41666666666</v>
@@ -6319,109 +6319,109 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.53</v>
+        <v>1.94</v>
       </c>
       <c r="M46" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>1.91</v>
+        <v>3.05</v>
       </c>
       <c r="O46" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="P46" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S46" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.91</v>
+        <v>2.69</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['45', '58']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.76</v>
+        <v>1.6</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45836.45833333334</v>
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="N47" t="n">
-        <v>3.05</v>
+        <v>7.9</v>
       </c>
       <c r="O47" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T47" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="U47" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="V47" t="n">
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.69</v>
+        <v>3.15</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['45', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45836.45833333334</v>
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.13</v>
+        <v>3.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="O48" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="P48" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="R48" t="n">
         <v>1.29</v>
       </c>
       <c r="S48" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="U48" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V48" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>1.5</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['16', '57']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['31', '12', '53', '68']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>2.04</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45836.45833333334</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,22 +6835,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="M50" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="N50" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="O50" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="P50" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R50" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="S50" t="n">
-        <v>2.85</v>
+        <v>5.25</v>
       </c>
       <c r="T50" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="U50" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>3.14</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.8</v>
+        <v>3.83</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['7', '22', '37', '39', '53', '85']</t>
+          <t>['51', '90+6', '87', '90+1']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AJ50" t="n">
-        <v>4.5</v>
+        <v>6.15</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45836.45833333334</v>
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X51" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['16', '57']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['31', '12', '53', '68']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
         <v>1.25</v>
       </c>
-      <c r="M51" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N51" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X51" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH51" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.29</v>
+        <v>1.78</v>
       </c>
       <c r="AJ51" t="n">
-        <v>3.44</v>
+        <v>2.04</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45836.45833333334</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,23 +7093,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>4</v>
       </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="M52" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="N52" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="P52" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R52" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="S52" t="n">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="T52" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="X52" t="n">
-        <v>9.300000000000001</v>
+        <v>3.14</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.83</v>
+        <v>1.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['51', '90+6', '87', '90+1']</t>
+          <t>['7', '22', '37', '39', '53', '85']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AH52" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AJ52" t="n">
-        <v>6.15</v>
+        <v>4.5</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45836.45833333334</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,19 +7222,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -7244,87 +7244,87 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45836.5</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,19 +7351,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.26</v>
+        <v>4.1</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="N54" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="X54" t="n">
-        <v>2.37</v>
+        <v>5.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7440,20 +7440,20 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['21', '49', '90+3', '88']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45836.5</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,109 +7480,109 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI55" t="n">
         <v>4</v>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O55" t="n">
-        <v>4</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X55" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>['21', '49', '90+3', '88']</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AJ55" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45836.5</v>
@@ -8263,30 +8263,30 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '59', '73', '78', '80']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,23 +9157,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>1</v>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
@@ -9183,65 +9183,65 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M68" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O68" t="n">
         <v>2.88</v>
       </c>
-      <c r="N68" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="O68" t="n">
-        <v>2.94</v>
-      </c>
       <c r="P68" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z68" t="n">
         <v>1.67</v>
       </c>
-      <c r="S68" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T68" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U68" t="n">
+      <c r="AA68" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB68" t="n">
         <v>1.22</v>
       </c>
-      <c r="V68" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X68" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AC68" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['23', '77']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -9250,16 +9250,16 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45836.66666666666</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,22 +9415,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -9441,83 +9441,83 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="N70" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="O70" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="P70" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="R70" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="S70" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="T70" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="U70" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V70" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG70" t="n">
         <v>1.36</v>
       </c>
-      <c r="X70" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>['23', '77']</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG70" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH70" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45836.66666666666</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,109 +9544,109 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
         <v>2</v>
       </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="M71" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="N71" t="n">
-        <v>2.25</v>
+        <v>2.97</v>
       </c>
       <c r="O71" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="P71" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.85</v>
+        <v>4.05</v>
       </c>
       <c r="R71" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S71" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T71" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U71" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V71" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W71" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="X71" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AA71" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AD71" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>['43', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['3', '39', '59', '82']</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AI71" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AJ71" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45836.70833333334</v>
@@ -9673,25 +9673,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9699,83 +9699,83 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.37</v>
+        <v>2.02</v>
       </c>
       <c r="M72" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N72" t="n">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="O72" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="P72" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.05</v>
+        <v>4.95</v>
       </c>
       <c r="R72" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="S72" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="T72" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="U72" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V72" t="n">
         <v>1.1</v>
       </c>
       <c r="W72" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="X72" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="AD72" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH72" t="n">
         <v>1.75</v>
       </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>['3', '39', '59', '82']</t>
-        </is>
-      </c>
-      <c r="AG72" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AI72" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ72" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45836.70833333334</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G73" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" t="n">
         <v>1</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.02</v>
+        <v>2.73</v>
       </c>
       <c r="M73" t="n">
-        <v>2.95</v>
+        <v>3.23</v>
       </c>
       <c r="N73" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="O73" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P73" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S73" t="n">
         <v>2.8</v>
       </c>
-      <c r="P73" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2.15</v>
-      </c>
       <c r="T73" t="n">
-        <v>4.35</v>
+        <v>2.96</v>
       </c>
       <c r="U73" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="V73" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="X73" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="Y73" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AA73" t="n">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.56</v>
+        <v>2.07</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['43', '56']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45836.70833333334</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,109 +10447,109 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
         <v>1</v>
       </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.68</v>
+        <v>1.88</v>
       </c>
       <c r="M78" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P78" t="n">
         <v>2.24</v>
       </c>
-      <c r="O78" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P78" t="n">
+      <c r="Q78" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X78" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD78" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q78" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R78" t="n">
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>['9', '61']</t>
+        </is>
+      </c>
+      <c r="AG78" t="n">
         <v>1.29</v>
       </c>
-      <c r="S78" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T78" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V78" t="n">
-        <v>1</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X78" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG78" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH78" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AI78" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ78" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45836.79166666666</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,109 +10576,109 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O79" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M79" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O79" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P79" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S79" t="n">
-        <v>3</v>
-      </c>
-      <c r="T79" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W79" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X79" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
         <v>1.22</v>
       </c>
-      <c r="X79" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB79" t="n">
+      <c r="AH79" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC79" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>['9', '61']</t>
-        </is>
-      </c>
-      <c r="AG79" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI79" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>45836.79166666666</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,19 +10834,19 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -10860,83 +10860,83 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="M81" t="n">
-        <v>2.87</v>
+        <v>5.5</v>
       </c>
       <c r="N81" t="n">
-        <v>4.39</v>
+        <v>7.25</v>
       </c>
       <c r="O81" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="P81" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
       <c r="R81" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="S81" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="T81" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="U81" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X81" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y81" t="n">
         <v>1.3</v>
       </c>
-      <c r="V81" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W81" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X81" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z81" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="AA81" t="n">
-        <v>4.1</v>
+        <v>1.67</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.73</v>
+        <v>2.58</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
       <c r="AG81" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>45836.8125</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,20 +10963,20 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
         <v>1</v>
       </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -10989,83 +10989,83 @@
         </is>
       </c>
       <c r="L82" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O82" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U82" t="n">
         <v>1.3</v>
       </c>
-      <c r="M82" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N82" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P82" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R82" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S82" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T82" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U82" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W82" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="X82" t="n">
-        <v>6.25</v>
+        <v>2.57</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z82" t="n">
-        <v>3.05</v>
+        <v>1.55</v>
       </c>
       <c r="AA82" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH82" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB82" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG82" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK82" s="3" t="n">
         <v>45836.8125</v>
@@ -11221,25 +11221,25 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -11247,83 +11247,83 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.64</v>
+        <v>1.75</v>
       </c>
       <c r="M84" t="n">
-        <v>3.07</v>
+        <v>3.7</v>
       </c>
       <c r="N84" t="n">
-        <v>2.41</v>
+        <v>3.95</v>
       </c>
       <c r="O84" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="P84" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q84" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R84" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S84" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="T84" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="U84" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V84" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W84" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="X84" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AA84" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['58', '86', '90+3']</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '40', '55']</t>
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AI84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>45836.85416666666</v>
@@ -11350,25 +11350,25 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G85" t="n">
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -11376,77 +11376,77 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.9</v>
+        <v>2.68</v>
       </c>
       <c r="M85" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="O85" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="P85" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="R85" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="S85" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="T85" t="n">
-        <v>2.35</v>
+        <v>2.72</v>
       </c>
       <c r="U85" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="V85" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W85" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X85" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.51</v>
+        <v>1.95</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>['45+4', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -11479,87 +11479,87 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.57</v>
+        <v>1.43</v>
       </c>
       <c r="M86" t="n">
-        <v>3.34</v>
+        <v>5.1</v>
       </c>
       <c r="N86" t="n">
-        <v>1.85</v>
+        <v>5.5</v>
       </c>
       <c r="O86" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="P86" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.45</v>
+        <v>5.25</v>
       </c>
       <c r="R86" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S86" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T86" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="U86" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="V86" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AD86" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11568,20 +11568,20 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>1.73</v>
+        <v>1.13</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AI86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
         <v>45836.85416666666</v>
@@ -11608,22 +11608,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>2</v>
@@ -11634,77 +11634,77 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="M87" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N87" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P87" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q87" t="n">
         <v>3.7</v>
       </c>
-      <c r="N87" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O87" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="P87" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>4.2</v>
-      </c>
       <c r="R87" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S87" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T87" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U87" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="V87" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W87" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X87" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD87" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>['58', '86', '90+3']</t>
+          <t>['11', '90']</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>['29', '40', '55']</t>
+          <t>['32', '45']</t>
         </is>
       </c>
       <c r="AG87" t="n">
         <v>1.25</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -11866,109 +11866,109 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
         <v>1</v>
       </c>
-      <c r="J89" t="n">
-        <v>2</v>
-      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.14</v>
+        <v>4.03</v>
       </c>
       <c r="M89" t="n">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="N89" t="n">
-        <v>3.02</v>
+        <v>1.8</v>
       </c>
       <c r="O89" t="n">
-        <v>2.88</v>
+        <v>4.45</v>
       </c>
       <c r="P89" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.6</v>
+        <v>2.49</v>
       </c>
       <c r="R89" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T89" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U89" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V89" t="n">
         <v>1.05</v>
       </c>
       <c r="W89" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X89" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AA89" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB89" t="n">
         <v>1.36</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>['11', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>['32', '45']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
         <v>45836.85416666666</v>
@@ -11995,109 +11995,109 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="N90" t="n">
-        <v>6.9</v>
+        <v>3.21</v>
       </c>
       <c r="O90" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="P90" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R90" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W90" t="n">
         <v>1.2</v>
       </c>
-      <c r="S90" t="n">
+      <c r="X90" t="n">
         <v>4.33</v>
       </c>
-      <c r="T90" t="n">
-        <v>2</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X90" t="n">
-        <v>6</v>
-      </c>
       <c r="Y90" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="Z90" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>['4504', '74']</t>
+        </is>
+      </c>
+      <c r="AG90" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ90" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG90" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AI90" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ90" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK90" s="3" t="n">
         <v>45836.85416666666</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,83 +12150,83 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="M91" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>3.88</v>
+        <v>2.3</v>
       </c>
       <c r="O91" t="n">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="P91" t="n">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
       <c r="Q91" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S91" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T91" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X91" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA91" t="n">
         <v>4.2</v>
       </c>
-      <c r="R91" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S91" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T91" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X91" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB91" t="n">
-        <v>1.92</v>
+        <v>1.22</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>['1', '72']</t>
+          <t>['39', '73']</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AH91" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AI91" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ91" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AK91" s="3" t="n">
         <v>45836.875</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,83 +12279,83 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.2</v>
+        <v>1.63</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N92" t="n">
-        <v>2.3</v>
+        <v>3.88</v>
       </c>
       <c r="O92" t="n">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="P92" t="n">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="R92" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="S92" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="T92" t="n">
-        <v>3.2</v>
+        <v>1.81</v>
       </c>
       <c r="U92" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="V92" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="X92" t="n">
-        <v>2.8</v>
+        <v>6.75</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AA92" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="AD92" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>['39', '73']</t>
+          <t>['1', '72']</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AI92" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ92" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AK92" s="3" t="n">
         <v>45836.875</v>
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="M93" t="n">
-        <v>4.1</v>
+        <v>3.21</v>
       </c>
       <c r="N93" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="O93" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P93" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S93" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T93" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U93" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V93" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W93" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X93" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AC93" t="n">
         <v>1.62</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,16 +12475,16 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH93" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK93" s="3" t="n">
         <v>45836.89583333334</v>
@@ -12511,25 +12511,25 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G94" t="n">
+        <v>3</v>
+      </c>
+      <c r="H94" t="n">
         <v>2</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>3</v>
       </c>
-      <c r="I94" t="n">
-        <v>1</v>
-      </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -12537,77 +12537,77 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.84</v>
+        <v>1.81</v>
       </c>
       <c r="M94" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N94" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="O94" t="n">
-        <v>3.4</v>
+        <v>2.47</v>
       </c>
       <c r="P94" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.69</v>
+        <v>3.45</v>
       </c>
       <c r="R94" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S94" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T94" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="U94" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="V94" t="n">
         <v>1.01</v>
       </c>
       <c r="W94" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X94" t="n">
-        <v>5.96</v>
+        <v>6.5</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.72</v>
+        <v>3.04</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>['44', '56']</t>
+          <t>['23', '25', '33']</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>['26', '77', '90+6']</t>
+          <t>['56', '59']</t>
         </is>
       </c>
       <c r="AG94" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -12640,25 +12640,25 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -12666,83 +12666,83 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="M95" t="n">
-        <v>3.11</v>
+        <v>3.55</v>
       </c>
       <c r="N95" t="n">
-        <v>3.53</v>
+        <v>2.5</v>
       </c>
       <c r="O95" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="P95" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R95" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S95" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T95" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U95" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="V95" t="n">
         <v>1.01</v>
       </c>
       <c r="W95" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X95" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="Y95" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC95" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z95" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AD95" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>['23', '25', '33']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>['56', '59']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AH95" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AI95" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
         <v>45836.89583333334</v>
@@ -12769,22 +12769,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3</v>
+      </c>
+      <c r="I96" t="n">
         <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>1</v>
@@ -12795,77 +12795,77 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="M96" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N96" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="O96" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P96" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="R96" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S96" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T96" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U96" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V96" t="n">
         <v>1.01</v>
       </c>
       <c r="W96" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X96" t="n">
-        <v>4.5</v>
+        <v>5.96</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['44', '56']</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['26', '77', '90+6']</t>
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -12898,19 +12898,19 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -12924,83 +12924,83 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="M97" t="n">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O97" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="P97" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="R97" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="T97" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="U97" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W97" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X97" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y97" t="n">
         <v>1.4</v>
       </c>
-      <c r="V97" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W97" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X97" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>1.79</v>
-      </c>
       <c r="Z97" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="AA97" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>['4502', '54']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH97" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
         <v>45836.97916666666</v>
@@ -13027,19 +13027,19 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -13053,83 +13053,83 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="M98" t="n">
-        <v>3.14</v>
+        <v>3.67</v>
       </c>
       <c r="N98" t="n">
-        <v>3.04</v>
+        <v>5</v>
       </c>
       <c r="O98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P98" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S98" t="n">
+        <v>3</v>
+      </c>
+      <c r="T98" t="n">
         <v>2.75</v>
       </c>
-      <c r="P98" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R98" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S98" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T98" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U98" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V98" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W98" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X98" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.86</v>
+        <v>3.15</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.84</v>
+        <v>1.31</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['4502', '54']</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AI98" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AJ98" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AK98" s="3" t="n">
         <v>45836.97916666666</v>
